--- a/Assets/Excel/任务配置表.xlsx
+++ b/Assets/Excel/任务配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="TaskInfo" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>f_id</t>
   </si>
@@ -82,7 +82,9 @@
   </si>
   <si>
     <t>任务奖励ID。""空字符串，则
-没有任务奖励</t>
+没有任务奖励
+奖励ID和数量
+（ID,数量）;（ID,数量）...</t>
   </si>
   <si>
     <t>下一节点任务ID。当前节点任务完成后的下一节点任务。若为-1，则说明该任务已完成；</t>
@@ -117,7 +119,7 @@
     <t>与流浪者对话</t>
   </si>
   <si>
-    <t>1,2</t>
+    <t>1,1000;2,2001</t>
   </si>
   <si>
     <t>1_-1</t>
@@ -130,6 +132,9 @@
   </si>
   <si>
     <t>用武力教他们做人</t>
+  </si>
+  <si>
+    <t>1,521</t>
   </si>
   <si>
     <t>2_-1</t>
@@ -774,7 +779,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -782,6 +787,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1096,16 +1110,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="2" width="24.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="31.2222222222222" customWidth="1"/>
-    <col min="4" max="4" width="29.8888888888889" customWidth="1"/>
-    <col min="5" max="5" width="27" customWidth="1"/>
-    <col min="6" max="6" width="33.7777777777778" customWidth="1"/>
-    <col min="7" max="7" width="38.8888888888889" customWidth="1"/>
-    <col min="8" max="8" width="42.7777777777778" customWidth="1"/>
-    <col min="9" max="9" width="25.4444444444444" customWidth="1"/>
+    <col min="1" max="2" width="24.1083333333333" customWidth="1"/>
+    <col min="3" max="3" width="31.225" customWidth="1"/>
+    <col min="4" max="4" width="29.8916666666667" customWidth="1"/>
+    <col min="5" max="5" width="27" style="3" customWidth="1"/>
+    <col min="6" max="6" width="33.775" customWidth="1"/>
+    <col min="7" max="7" width="38.8916666666667" customWidth="1"/>
+    <col min="8" max="8" width="42.775" customWidth="1"/>
+    <col min="9" max="9" width="25.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:9">
@@ -1121,7 +1135,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1150,7 +1164,7 @@
       <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -1170,8 +1184,9 @@
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="E3" s="4"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="4" s="1" customFormat="1" ht="90" customHeight="1" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -1184,7 +1199,7 @@
       <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -1213,7 +1228,7 @@
       <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1"/>
+      <c r="E5" s="4"/>
       <c r="F5" s="1" t="s">
         <v>24</v>
       </c>
@@ -1236,7 +1251,7 @@
       <c r="D6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -1259,11 +1274,11 @@
       <c r="D7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="1">
-        <v>1</v>
+      <c r="E7" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7" s="1">
         <v>3</v>
@@ -1280,12 +1295,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="16.4444444444444" customWidth="1"/>
-    <col min="2" max="2" width="28.4444444444444" customWidth="1"/>
+    <col min="1" max="1" width="16.4416666666667" customWidth="1"/>
+    <col min="2" max="2" width="28.4416666666667" customWidth="1"/>
     <col min="3" max="3" width="27.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="28.4444444444444" customWidth="1"/>
+    <col min="4" max="4" width="28.4416666666667" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1294,13 +1309,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:4">
@@ -1322,18 +1337,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="72" spans="1:4">
+    <row r="4" s="1" customFormat="1" ht="67.5" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">

--- a/Assets/Excel/任务配置表.xlsx
+++ b/Assets/Excel/任务配置表.xlsx
@@ -119,7 +119,7 @@
     <t>与流浪者对话</t>
   </si>
   <si>
-    <t>1,1000;2,2001</t>
+    <t>10001,1000;10002,2001</t>
   </si>
   <si>
     <t>1_-1</t>
@@ -134,7 +134,7 @@
     <t>用武力教他们做人</t>
   </si>
   <si>
-    <t>1,521</t>
+    <t>10001,521</t>
   </si>
   <si>
     <t>2_-1</t>
